--- a/conformance/fixtures/011-text-date-format/data.xlsx
+++ b/conformance/fixtures/011-text-date-format/data.xlsx
@@ -404,7 +404,7 @@
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" s="1">
-        <v>46144.625</v>
+        <v>46145</v>
       </c>
     </row>
   </sheetData>
